--- a/results/main/Figure_2_summary.xlsx
+++ b/results/main/Figure_2_summary.xlsx
@@ -7,13 +7,12 @@
   </bookViews>
   <sheets>
     <sheet name="Figure 2 summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="High-power subfields" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">result</t>
   </si>
@@ -37,30 +36,6 @@
   </si>
   <si>
     <t xml:space="preserve">Share of adequately powered estimates greater than 20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_high_power_meta_analyses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health, Toxicology and Mutagenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Science and Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nature and Landscape Conservation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Chemistry</t>
   </si>
 </sst>
 </file>
@@ -463,113 +438,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C2" t="n">
-        <v>87</v>
-      </c>
-      <c r="D2" t="n">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C3" t="n">
-        <v>87</v>
-      </c>
-      <c r="D3" t="n">
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C4" t="n">
-        <v>87</v>
-      </c>
-      <c r="D4" t="n">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>87</v>
-      </c>
-      <c r="D5" t="n">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>87</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>87</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
 </file>